--- a/outputs/Estadistica Ejercicio/Heatmap/Llamadas911.xlsx
+++ b/outputs/Estadistica Ejercicio/Heatmap/Llamadas911.xlsx
@@ -671,10 +671,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4042</v>
+        <v>0.0449</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3023</v>
+        <v>1.6616</v>
       </c>
       <c r="D2" t="n">
         <v>2.1107</v>
@@ -709,10 +709,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>0.369</v>
+        <v>0.0217</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9769</v>
+        <v>1.3242</v>
       </c>
       <c r="D3" t="n">
         <v>1.1288</v>
@@ -747,10 +747,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="n">
-        <v>2.6065</v>
+        <v>0.7705</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7539</v>
+        <v>7.5899</v>
       </c>
       <c r="D4" t="n">
         <v>3.7376</v>
@@ -785,10 +785,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6788</v>
+        <v>0.1939</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3575</v>
+        <v>1.8423</v>
       </c>
       <c r="D5" t="n">
         <v>1.9393</v>
@@ -823,10 +823,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>1.4837</v>
+        <v>0.4239</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3913</v>
+        <v>4.451</v>
       </c>
       <c r="D6" t="n">
         <v>3.3913</v>
@@ -861,10 +861,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1044</v>
+        <v>0.0522</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3653</v>
+        <v>0.4175</v>
       </c>
       <c r="D7" t="n">
         <v>0.3131</v>
@@ -899,10 +899,10 @@
         <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>2.3115</v>
+        <v>0.6377</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8333</v>
+        <v>3.5071</v>
       </c>
       <c r="D8" t="n">
         <v>1.355</v>
@@ -937,10 +937,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>3.2776</v>
+        <v>1.0497</v>
       </c>
       <c r="C9" t="n">
-        <v>4.4986</v>
+        <v>6.7265</v>
       </c>
       <c r="D9" t="n">
         <v>3.7274</v>
@@ -975,10 +975,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>2.0619</v>
+        <v>0.6661</v>
       </c>
       <c r="C10" t="n">
-        <v>4.3775</v>
+        <v>5.7732</v>
       </c>
       <c r="D10" t="n">
         <v>4.6947</v>
@@ -1013,10 +1013,10 @@
         <v>21</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3533</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4543</v>
+        <v>0.8076</v>
       </c>
       <c r="D11" t="n">
         <v>0.1514</v>
@@ -1051,10 +1051,10 @@
         <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>1.6168</v>
+        <v>0.4322</v>
       </c>
       <c r="C12" t="n">
-        <v>5.8108</v>
+        <v>6.9954</v>
       </c>
       <c r="D12" t="n">
         <v>3.2015</v>
@@ -1089,10 +1089,10 @@
         <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>1.0951</v>
+        <v>0.4646</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4601</v>
+        <v>2.0906</v>
       </c>
       <c r="D13" t="n">
         <v>1.2942</v>
@@ -1165,10 +1165,10 @@
         <v>25</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1029</v>
+        <v>0.1544</v>
       </c>
       <c r="D15" t="n">
         <v>0.0515</v>
@@ -1203,10 +1203,10 @@
         <v>26</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3856</v>
+        <v>0.1542</v>
       </c>
       <c r="C16" t="n">
-        <v>3.0848</v>
+        <v>3.3161</v>
       </c>
       <c r="D16" t="n">
         <v>1.6195</v>
@@ -1241,10 +1241,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="n">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1746</v>
+        <v>0.3056</v>
       </c>
       <c r="D17" t="n">
         <v>0.1746</v>
@@ -1279,10 +1279,10 @@
         <v>28</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2644</v>
+        <v>0.1058</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6346</v>
+        <v>0.7933</v>
       </c>
       <c r="D18" t="n">
         <v>0.5817</v>
@@ -1317,10 +1317,10 @@
         <v>29</v>
       </c>
       <c r="B19" t="n">
-        <v>1.5723</v>
+        <v>0.3972</v>
       </c>
       <c r="C19" t="n">
-        <v>2.2343</v>
+        <v>3.4094</v>
       </c>
       <c r="D19" t="n">
         <v>2.5653</v>
@@ -1355,10 +1355,10 @@
         <v>30</v>
       </c>
       <c r="B20" t="n">
-        <v>0.857</v>
+        <v>0.2521</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9744</v>
+        <v>3.5794</v>
       </c>
       <c r="D20" t="n">
         <v>2.6215</v>
@@ -1431,10 +1431,10 @@
         <v>32</v>
       </c>
       <c r="B22" t="n">
-        <v>0.8567</v>
+        <v>0.3295</v>
       </c>
       <c r="C22" t="n">
-        <v>2.57</v>
+        <v>3.0972</v>
       </c>
       <c r="D22" t="n">
         <v>2.57</v>
@@ -1469,10 +1469,10 @@
         <v>33</v>
       </c>
       <c r="B23" t="n">
-        <v>1.4737</v>
+        <v>0.4298</v>
       </c>
       <c r="C23" t="n">
-        <v>5.4037</v>
+        <v>6.4477</v>
       </c>
       <c r="D23" t="n">
         <v>4.8511</v>
@@ -1507,10 +1507,10 @@
         <v>34</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9104</v>
+        <v>0.3311</v>
       </c>
       <c r="C24" t="n">
-        <v>3.0622</v>
+        <v>3.6416</v>
       </c>
       <c r="D24" t="n">
         <v>1.8484</v>
@@ -1545,10 +1545,10 @@
         <v>35</v>
       </c>
       <c r="B25" t="n">
-        <v>0.4544</v>
+        <v>0.1704</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4199</v>
+        <v>1.7039</v>
       </c>
       <c r="D25" t="n">
         <v>1.0223</v>
@@ -1583,10 +1583,10 @@
         <v>36</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0967</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0967</v>
+        <v>0.1935</v>
       </c>
       <c r="D26" t="n">
         <v>0.0967</v>
@@ -1659,10 +1659,10 @@
         <v>38</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0875</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0438</v>
+        <v>0.1313</v>
       </c>
       <c r="D28" t="n">
         <v>0.0438</v>
@@ -1697,10 +1697,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8045</v>
+        <v>0.1499</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5223</v>
+        <v>2.177</v>
       </c>
       <c r="D29" t="n">
         <v>0.7888</v>
@@ -1735,10 +1735,10 @@
         <v>40</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8856</v>
+        <v>0.2319</v>
       </c>
       <c r="C30" t="n">
-        <v>1.9188</v>
+        <v>2.5725</v>
       </c>
       <c r="D30" t="n">
         <v>2.0875</v>
@@ -1773,10 +1773,10 @@
         <v>41</v>
       </c>
       <c r="B31" t="n">
-        <v>1.3786</v>
+        <v>0.3953</v>
       </c>
       <c r="C31" t="n">
-        <v>2.5037</v>
+        <v>3.4869</v>
       </c>
       <c r="D31" t="n">
         <v>1.3177</v>
@@ -1811,10 +1811,10 @@
         <v>42</v>
       </c>
       <c r="B32" t="n">
-        <v>0.4882</v>
+        <v>0.0814</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7323</v>
+        <v>1.1391</v>
       </c>
       <c r="D32" t="n">
         <v>0.6509</v>
@@ -1849,10 +1849,10 @@
         <v>43</v>
       </c>
       <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
         <v>0.095</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0.095</v>
@@ -1925,10 +1925,10 @@
         <v>45</v>
       </c>
       <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
         <v>0.1018</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0.1018</v>
@@ -2001,10 +2001,10 @@
         <v>47</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3059</v>
+        <v>0.1529</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4588</v>
+        <v>0.6117</v>
       </c>
       <c r="D37" t="n">
         <v>1.147</v>
@@ -2039,10 +2039,10 @@
         <v>48</v>
       </c>
       <c r="B38" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="C38" t="n">
         <v>0.3339</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.1431</v>
       </c>
       <c r="D38" t="n">
         <v>0.3816</v>
@@ -2077,10 +2077,10 @@
         <v>49</v>
       </c>
       <c r="B39" t="n">
-        <v>5.5882</v>
+        <v>1.8496</v>
       </c>
       <c r="C39" t="n">
-        <v>11.4624</v>
+        <v>15.2011</v>
       </c>
       <c r="D39" t="n">
         <v>8.4834</v>
@@ -2153,10 +2153,10 @@
         <v>51</v>
       </c>
       <c r="B41" t="n">
-        <v>1.4661</v>
+        <v>0.6981</v>
       </c>
       <c r="C41" t="n">
-        <v>4.468</v>
+        <v>5.236</v>
       </c>
       <c r="D41" t="n">
         <v>2.3736</v>
@@ -2191,10 +2191,10 @@
         <v>52</v>
       </c>
       <c r="B42" t="n">
-        <v>1.9271</v>
+        <v>0.4659</v>
       </c>
       <c r="C42" t="n">
-        <v>3.1765</v>
+        <v>4.6377</v>
       </c>
       <c r="D42" t="n">
         <v>2.0753</v>
@@ -2229,10 +2229,10 @@
         <v>53</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1727</v>
+        <v>0.0864</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5182</v>
+        <v>0.6046</v>
       </c>
       <c r="D43" t="n">
         <v>0.2591</v>
@@ -2305,10 +2305,10 @@
         <v>55</v>
       </c>
       <c r="B45" t="n">
-        <v>0.472</v>
+        <v>0.059</v>
       </c>
       <c r="C45" t="n">
-        <v>1.0031</v>
+        <v>1.4161</v>
       </c>
       <c r="D45" t="n">
         <v>1.8881</v>
@@ -2343,10 +2343,10 @@
         <v>56</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6455</v>
+        <v>0.4303</v>
       </c>
       <c r="C46" t="n">
-        <v>1.6138</v>
+        <v>1.8289</v>
       </c>
       <c r="D46" t="n">
         <v>3.2275</v>
@@ -2381,10 +2381,10 @@
         <v>57</v>
       </c>
       <c r="B47" t="n">
-        <v>10.3299</v>
+        <v>3.2482</v>
       </c>
       <c r="C47" t="n">
-        <v>16.8358</v>
+        <v>23.9175</v>
       </c>
       <c r="D47" t="n">
         <v>13.1008</v>
@@ -2495,10 +2495,10 @@
         <v>60</v>
       </c>
       <c r="B50" t="n">
-        <v>1.8189</v>
+        <v>0.5499</v>
       </c>
       <c r="C50" t="n">
-        <v>2.961</v>
+        <v>4.2299</v>
       </c>
       <c r="D50" t="n">
         <v>2.961</v>
@@ -2533,10 +2533,10 @@
         <v>61</v>
       </c>
       <c r="B51" t="n">
-        <v>0.4233</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2117</v>
+        <v>0.635</v>
       </c>
       <c r="D51" t="n">
         <v>0.4233</v>
@@ -2571,10 +2571,10 @@
         <v>62</v>
       </c>
       <c r="B52" t="n">
-        <v>1.8256</v>
+        <v>0.5657</v>
       </c>
       <c r="C52" t="n">
-        <v>3.4712</v>
+        <v>4.7312</v>
       </c>
       <c r="D52" t="n">
         <v>3.4712</v>
@@ -2609,10 +2609,10 @@
         <v>63</v>
       </c>
       <c r="B53" t="n">
-        <v>0.904</v>
+        <v>0.3955</v>
       </c>
       <c r="C53" t="n">
-        <v>1.243</v>
+        <v>1.7515</v>
       </c>
       <c r="D53" t="n">
         <v>0.678</v>
@@ -2647,10 +2647,10 @@
         <v>64</v>
       </c>
       <c r="B54" t="n">
-        <v>0.5715</v>
+        <v>0.2078</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2338</v>
+        <v>0.5975</v>
       </c>
       <c r="D54" t="n">
         <v>0.1559</v>
@@ -2685,10 +2685,10 @@
         <v>65</v>
       </c>
       <c r="B55" t="n">
-        <v>1.0599</v>
+        <v>0.2718</v>
       </c>
       <c r="C55" t="n">
-        <v>2.2557</v>
+        <v>3.0438</v>
       </c>
       <c r="D55" t="n">
         <v>1.7393</v>
@@ -2723,10 +2723,10 @@
         <v>66</v>
       </c>
       <c r="B56" t="n">
-        <v>2.8311</v>
+        <v>0.7836</v>
       </c>
       <c r="C56" t="n">
-        <v>5.1819</v>
+        <v>7.2293</v>
       </c>
       <c r="D56" t="n">
         <v>4.7774</v>
@@ -2761,10 +2761,10 @@
         <v>67</v>
       </c>
       <c r="B57" t="n">
-        <v>0.8184</v>
+        <v>0.3274</v>
       </c>
       <c r="C57" t="n">
-        <v>1.3094</v>
+        <v>1.8004</v>
       </c>
       <c r="D57" t="n">
         <v>1.1457</v>
@@ -2799,10 +2799,10 @@
         <v>68</v>
       </c>
       <c r="B58" t="n">
-        <v>1.3208</v>
+        <v>0.5283</v>
       </c>
       <c r="C58" t="n">
-        <v>2.6417</v>
+        <v>3.4342</v>
       </c>
       <c r="D58" t="n">
         <v>5.6796</v>
@@ -2837,10 +2837,10 @@
         <v>69</v>
       </c>
       <c r="B59" t="n">
-        <v>0.344</v>
+        <v>0.0573</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7454</v>
+        <v>1.0321</v>
       </c>
       <c r="D59" t="n">
         <v>0.5734</v>
@@ -2875,10 +2875,10 @@
         <v>70</v>
       </c>
       <c r="B60" t="n">
-        <v>0.7103</v>
+        <v>0.2105</v>
       </c>
       <c r="C60" t="n">
-        <v>0.684</v>
+        <v>1.1839</v>
       </c>
       <c r="D60" t="n">
         <v>0.6577</v>
@@ -2913,10 +2913,10 @@
         <v>71</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1143</v>
+        <v>0.0571</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7999</v>
+        <v>0.857</v>
       </c>
       <c r="D61" t="n">
         <v>0.6856</v>
@@ -2951,10 +2951,10 @@
         <v>72</v>
       </c>
       <c r="B62" t="n">
-        <v>3.627</v>
+        <v>1.1379</v>
       </c>
       <c r="C62" t="n">
-        <v>5.6361</v>
+        <v>8.1252</v>
       </c>
       <c r="D62" t="n">
         <v>5.4227</v>
@@ -2989,10 +2989,10 @@
         <v>73</v>
       </c>
       <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
         <v>0.032</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0.064</v>
@@ -3027,10 +3027,10 @@
         <v>74</v>
       </c>
       <c r="B64" t="n">
-        <v>3.1917</v>
+        <v>1.2259</v>
       </c>
       <c r="C64" t="n">
-        <v>5.7208</v>
+        <v>7.6867</v>
       </c>
       <c r="D64" t="n">
         <v>4.7048</v>
@@ -3065,10 +3065,10 @@
         <v>75</v>
       </c>
       <c r="B65" t="n">
-        <v>0.554</v>
+        <v>0.1847</v>
       </c>
       <c r="C65" t="n">
-        <v>1.7544</v>
+        <v>2.1237</v>
       </c>
       <c r="D65" t="n">
         <v>1.2004</v>
@@ -3103,10 +3103,10 @@
         <v>76</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9347</v>
+        <v>0.085</v>
       </c>
       <c r="C66" t="n">
-        <v>2.4643</v>
+        <v>3.3141</v>
       </c>
       <c r="D66" t="n">
         <v>2.7192</v>
@@ -3141,10 +3141,10 @@
         <v>77</v>
       </c>
       <c r="B67" t="n">
-        <v>1.2515</v>
+        <v>0.3809</v>
       </c>
       <c r="C67" t="n">
-        <v>3.029</v>
+        <v>3.8996</v>
       </c>
       <c r="D67" t="n">
         <v>2.7751</v>
@@ -3179,10 +3179,10 @@
         <v>78</v>
       </c>
       <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
         <v>0.1395</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>0.2789</v>
@@ -3217,10 +3217,10 @@
         <v>79</v>
       </c>
       <c r="B69" t="n">
-        <v>2.5133</v>
+        <v>0.9863</v>
       </c>
       <c r="C69" t="n">
-        <v>8.2352</v>
+        <v>9.7622</v>
       </c>
       <c r="D69" t="n">
         <v>4.4741</v>
@@ -3255,10 +3255,10 @@
         <v>80</v>
       </c>
       <c r="B70" t="n">
-        <v>2.7797</v>
+        <v>0.9965</v>
       </c>
       <c r="C70" t="n">
-        <v>5.9789</v>
+        <v>7.7621</v>
       </c>
       <c r="D70" t="n">
         <v>3.1468</v>
@@ -3331,10 +3331,10 @@
         <v>82</v>
       </c>
       <c r="B72" t="n">
-        <v>3.4194</v>
+        <v>1.3498</v>
       </c>
       <c r="C72" t="n">
-        <v>3.7794</v>
+        <v>5.849</v>
       </c>
       <c r="D72" t="n">
         <v>4.6792</v>
@@ -3369,10 +3369,10 @@
         <v>83</v>
       </c>
       <c r="B73" t="n">
-        <v>0.106</v>
+        <v>0.0265</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1591</v>
+        <v>0.2386</v>
       </c>
       <c r="D73" t="n">
         <v>0.053</v>
@@ -3407,10 +3407,10 @@
         <v>84</v>
       </c>
       <c r="B74" t="n">
-        <v>1.9563</v>
+        <v>0.3843</v>
       </c>
       <c r="C74" t="n">
-        <v>4.6461</v>
+        <v>6.2181</v>
       </c>
       <c r="D74" t="n">
         <v>3.2837</v>
@@ -3445,10 +3445,10 @@
         <v>85</v>
       </c>
       <c r="B75" t="n">
-        <v>1.6852</v>
+        <v>0.7022</v>
       </c>
       <c r="C75" t="n">
-        <v>3.6982</v>
+        <v>4.6812</v>
       </c>
       <c r="D75" t="n">
         <v>2.5747</v>
@@ -3483,10 +3483,10 @@
         <v>86</v>
       </c>
       <c r="B76" t="n">
-        <v>4.0397</v>
+        <v>1.2944</v>
       </c>
       <c r="C76" t="n">
-        <v>6.6894</v>
+        <v>9.4347</v>
       </c>
       <c r="D76" t="n">
         <v>6.8197</v>
@@ -3521,10 +3521,10 @@
         <v>87</v>
       </c>
       <c r="B77" t="n">
-        <v>6.266</v>
+        <v>1.96</v>
       </c>
       <c r="C77" t="n">
-        <v>9.5445</v>
+        <v>13.8505</v>
       </c>
       <c r="D77" t="n">
         <v>9.7227</v>
@@ -3559,10 +3559,10 @@
         <v>88</v>
       </c>
       <c r="B78" t="n">
-        <v>1.9951</v>
+        <v>0.8441</v>
       </c>
       <c r="C78" t="n">
-        <v>3.2228</v>
+        <v>4.3738</v>
       </c>
       <c r="D78" t="n">
         <v>3.453</v>
@@ -3635,10 +3635,10 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1426</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2851</v>
+        <v>0.4277</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -3711,10 +3711,10 @@
         <v>92</v>
       </c>
       <c r="B82" t="n">
-        <v>1.625</v>
+        <v>0.4718</v>
       </c>
       <c r="C82" t="n">
-        <v>2.0967</v>
+        <v>3.2499</v>
       </c>
       <c r="D82" t="n">
         <v>1.1794</v>
@@ -3749,10 +3749,10 @@
         <v>93</v>
       </c>
       <c r="B83" t="n">
-        <v>3.0313</v>
+        <v>1.1659</v>
       </c>
       <c r="C83" t="n">
-        <v>3.8707</v>
+        <v>5.7361</v>
       </c>
       <c r="D83" t="n">
         <v>4.6169</v>
@@ -3787,10 +3787,10 @@
         <v>94</v>
       </c>
       <c r="B84" t="n">
-        <v>2.0896</v>
+        <v>0.7599</v>
       </c>
       <c r="C84" t="n">
-        <v>6.2688</v>
+        <v>7.5985</v>
       </c>
       <c r="D84" t="n">
         <v>5.4744</v>
@@ -3825,10 +3825,10 @@
         <v>95</v>
       </c>
       <c r="B85" t="n">
-        <v>1.0269</v>
+        <v>0.4007</v>
       </c>
       <c r="C85" t="n">
-        <v>1.7532</v>
+        <v>2.3793</v>
       </c>
       <c r="D85" t="n">
         <v>1.0269</v>
